--- a/public/excel-converter/examples/30_병합셀_타회사노임양식.xlsx
+++ b/public/excel-converter/examples/30_병합셀_타회사노임양식.xlsx
@@ -4,6 +4,9 @@
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="병합노임명세서" sheetId="1" r:id="Rfe0c8f80a1264551"/>
   </x:sheets>
+  <x:definedNames>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="0">'병합노임명세서'!$A$1:$G$15</x:definedName>
+  </x:definedNames>
 </x:workbook>
 </file>
 
@@ -377,6 +380,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:pageSetUpPr fitToPage="1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="23" hidden="0" customWidth="1"/>
@@ -596,5 +602,6 @@
     <x:mergeCell ref="A15:G15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </x:worksheet>
 </file>